--- a/property_management_forms/017_tenant_move_out_checklist--property_management_forms.xlsx
+++ b/property_management_forms/017_tenant_move_out_checklist--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Property Status</t>
+          <t>Current Property Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Notice Period</t>
+          <t>Notice Period (Days)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -669,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>condition_of_move_out</t>
+          <t>lease_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Condition Of Move Out</t>
+          <t>Lease Status</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>damages</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Damages</t>
+          <t>Property Type</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>move_in_date_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Move In Date 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>utilities_billed</t>
+          <t>move_out_date_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Utilities Billed</t>
+          <t>Move Out Date 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rent_paid</t>
+          <t>notice_period_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rent Paid</t>
+          <t>Notice Period 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,46 +860,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lease_status</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lease Status</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>utilities_billed_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Property Type</t>
+          <t>Utilities Billed 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>rent_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Rent 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>security_deposit</t>
+          <t>security_deposit_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Security Deposit</t>
+          <t>Security Deposit 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notice_period</t>
+          <t>notice_period_days_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notice Period</t>
+          <t>Notice Period Days 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>move_in_date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Move In Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>move_out_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Move Out Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>notice_period_days</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Notice Period</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>utilities_paid</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Utilities Paid</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>utilities_billed</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Utilities Billed</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1148,46 +1033,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>occupied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Occupied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>condition_of_move_out_choices</t>
+          <t>property_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>condition_of_move_out_choices</t>
+          <t>property_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1199,53 +1084,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>utilities_paid_choices</t>
+          <t>condition_of_move_out_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>utilities_paid_choices</t>
+          <t>condition_of_move_out_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>utilities_billed_choices</t>
+          <t>utilities_paid_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1147,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>utilities_billed_choices</t>
+          <t>utilities_paid_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1164,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>utilities_billed_choices</t>
+          <t>utilities_paid_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>utilities_choices</t>
+          <t>utilities_billed_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1198,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>utilities_choices</t>
+          <t>utilities_billed_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1215,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>utilities_choices</t>
+          <t>utilities_billed_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,253 +1232,168 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>utilities_billed_choices</t>
+          <t>lease_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>utilities_billed_choices</t>
+          <t>lease_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>utilities_billed_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rent_paid_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rent_paid_choices</t>
+          <t>utilities_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lease_status_choices</t>
+          <t>utilities_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Electricity</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lease_status_choices</t>
+          <t>utilities_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>utilities_billed_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Residential</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>utilities_billed_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>commercial</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Electricity</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>utilities_paid_choices</t>
+          <t>utilities_billed_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>utilities_paid_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>utilities_paid_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>utilities_billed_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>gas</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>utilities_billed_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>utilities_billed_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
